--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/26,10,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/26,10,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\26,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26E6D71-DFA5-4810-B7CB-59079634B596}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8EA1C6-10C4-458B-A6B2-720E037EAFEA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -875,27 +875,27 @@
         <v>10</v>
       </c>
       <c r="B16" s="4">
-        <f>SUM(B2:B15)</f>
+        <f t="shared" ref="B16:G16" si="1">SUM(B2:B15)</f>
         <v>30211</v>
       </c>
       <c r="C16" s="4">
-        <f>SUM(C2:C15)</f>
+        <f t="shared" si="1"/>
         <v>8308</v>
       </c>
       <c r="D16" s="4">
-        <f>SUM(D2:D15)</f>
+        <f t="shared" si="1"/>
         <v>17765</v>
       </c>
       <c r="E16" s="4">
-        <f>SUM(E2:E15)</f>
+        <f t="shared" si="1"/>
         <v>3289</v>
       </c>
       <c r="F16" s="4">
-        <f>SUM(F2:F15)</f>
+        <f t="shared" si="1"/>
         <v>849</v>
       </c>
       <c r="G16" s="4">
-        <f>SUM(G2:G15)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -924,15 +924,15 @@
         <v>17</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" ref="D19:F19" si="1">IF(ROUNDUP(D16/500,0)&gt;32,32,ROUNDUP(D16/500,0))</f>
+        <f t="shared" ref="D19:F19" si="2">IF(ROUNDUP(D16/500,0)&gt;32,32,ROUNDUP(D16/500,0))</f>
         <v>32</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
